--- a/public/FormatoVacaciones.xlsx
+++ b/public/FormatoVacaciones.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RubenSA\Documents\proyecto plataforma RH\Incidencias nuevo\CHC_Incidencias_1_6_modificado\incidencias2.0.1\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RubenSA\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF02F65-896F-4252-B136-E8C3AF89B4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4E479C7-D3A6-4639-8C4E-8DEBCF149E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0AB998DF-8648-4B24-8913-C7EA21C75923}"/>
+    <workbookView xWindow="-28920" yWindow="-795" windowWidth="29040" windowHeight="15720" xr2:uid="{0AB998DF-8648-4B24-8913-C7EA21C75923}"/>
   </bookViews>
   <sheets>
     <sheet name="Solicitud de Vacaciones (3)" sheetId="1" r:id="rId1"/>
@@ -1445,9 +1445,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2537012</xdr:colOff>
+      <xdr:colOff>2533202</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>175112</xdr:rowOff>
+      <xdr:rowOff>171302</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1503,9 +1503,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>2122619</xdr:colOff>
+      <xdr:colOff>2120714</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>49650</xdr:rowOff>
+      <xdr:rowOff>53460</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1894,7 +1894,9 @@
       <c r="E4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="9"/>
+      <c r="F4" s="9">
+        <v>44896</v>
+      </c>
       <c r="G4"/>
     </row>
     <row r="5" spans="2:7" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2188,7 +2190,9 @@
       <c r="E39" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F39" s="9"/>
+      <c r="F39" s="9">
+        <v>44896</v>
+      </c>
       <c r="G39"/>
     </row>
     <row r="40" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
